--- a/outputs_xlsx_solution/test_new3.4-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide.xlsx
@@ -77,7 +77,7 @@
     <t>fmul F3, F3, F1</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
   </si>
   <si>
     <t>fadd F4, F1, F1</t>
@@ -89,10 +89,13 @@
     <t>fsd F4, 0(X1)</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>add X1, X1, X4</t>
@@ -107,6 +110,9 @@
     <t>bne X5, X0, 36</t>
   </si>
   <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
     <t>fadd F2, F2, F4</t>
   </si>
   <si>
@@ -125,13 +131,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -633,7 +657,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -656,10 +680,10 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -682,10 +706,10 @@
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -708,10 +732,10 @@
         <v>14</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -737,7 +761,7 @@
         <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -757,19 +781,19 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -789,19 +813,19 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -821,22 +845,22 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -856,22 +880,22 @@
         <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
         <v>18</v>
       </c>
       <c r="P10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -890,20 +914,29 @@
       <c r="G11" t="s">
         <v>9</v>
       </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
       <c r="K11" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -923,22 +956,22 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -958,16 +991,16 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="s">
         <v>18</v>
       </c>
       <c r="T13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -978,7 +1011,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -993,7 +1026,7 @@
         <v>18</v>
       </c>
       <c r="T14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -1004,7 +1037,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1019,7 +1052,7 @@
         <v>18</v>
       </c>
       <c r="T15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1030,7 +1063,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1039,16 +1072,16 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N16" t="s">
         <v>18</v>
       </c>
-      <c r="T16" t="s">
-        <v>18</v>
+      <c r="U16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1059,7 +1092,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
@@ -1068,16 +1101,16 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O17" t="s">
         <v>18</v>
       </c>
-      <c r="T17" t="s">
-        <v>18</v>
+      <c r="U17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1100,13 +1133,16 @@
         <v>14</v>
       </c>
       <c r="R18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T18" t="s">
         <v>18</v>
+      </c>
+      <c r="U18" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -1126,22 +1162,22 @@
         <v>9</v>
       </c>
       <c r="Q19" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="W19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -1161,16 +1197,16 @@
         <v>9</v>
       </c>
       <c r="Q20" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U20" t="s">
         <v>18</v>
       </c>
       <c r="X20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -1181,7 +1217,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
         <v>5</v>
@@ -1190,16 +1226,16 @@
         <v>9</v>
       </c>
       <c r="Q21" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S21" t="s">
         <v>18</v>
       </c>
       <c r="X21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -1210,7 +1246,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P22" t="s">
         <v>5</v>
@@ -1219,16 +1255,16 @@
         <v>9</v>
       </c>
       <c r="R22" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="S22" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T22" t="s">
         <v>18</v>
       </c>
       <c r="X22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1239,7 +1275,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P23" t="s">
         <v>5</v>
@@ -1248,59 +1284,56 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>14</v>
-      </c>
-      <c r="X23" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="T23" t="s">
+        <v>14</v>
+      </c>
+      <c r="U23" t="s">
+        <v>18</v>
       </c>
       <c r="Y23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
+      <c r="P24" t="s">
+        <v>5</v>
       </c>
       <c r="Q24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="R24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" t="s">
-        <v>14</v>
-      </c>
-      <c r="T24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V24" t="s">
-        <v>19</v>
-      </c>
-      <c r="W24" t="s">
         <v>18</v>
       </c>
       <c r="Y24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="s">
         <v>5</v>
@@ -1309,33 +1342,33 @@
         <v>9</v>
       </c>
       <c r="S25" t="s">
-        <v>14</v>
-      </c>
-      <c r="X25" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="T25" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" t="s">
+        <v>14</v>
+      </c>
+      <c r="W25" t="s">
+        <v>18</v>
       </c>
       <c r="Y25" t="s">
         <v>19</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="s">
         <v>5</v>
@@ -1344,27 +1377,36 @@
         <v>9</v>
       </c>
       <c r="S26" t="s">
-        <v>14</v>
-      </c>
-      <c r="W26" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="T26" t="s">
+        <v>20</v>
       </c>
       <c r="X26" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>14</v>
       </c>
       <c r="AB26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="s">
         <v>5</v>
@@ -1372,54 +1414,54 @@
       <c r="R27" t="s">
         <v>9</v>
       </c>
-      <c r="S27" t="s">
-        <v>14</v>
-      </c>
       <c r="T27" t="s">
-        <v>19</v>
-      </c>
-      <c r="U27" t="s">
+        <v>20</v>
+      </c>
+      <c r="W27" t="s">
+        <v>14</v>
+      </c>
+      <c r="X27" t="s">
         <v>18</v>
       </c>
       <c r="AB27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="Q28" t="s">
+        <v>5</v>
+      </c>
       <c r="R28" t="s">
-        <v>5</v>
-      </c>
-      <c r="S28" t="s">
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="U28" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V28" t="s">
         <v>18</v>
       </c>
       <c r="AB28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -1431,94 +1473,85 @@
         <v>9</v>
       </c>
       <c r="T29" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="V29" t="s">
+        <v>14</v>
+      </c>
+      <c r="W29" t="s">
+        <v>18</v>
       </c>
       <c r="AB29" t="s">
         <v>19</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="R30" t="s">
+        <v>5</v>
       </c>
       <c r="S30" t="s">
-        <v>5</v>
-      </c>
-      <c r="T30" t="s">
         <v>9</v>
       </c>
       <c r="U30" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W30" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X30" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z30" t="s">
         <v>18</v>
       </c>
       <c r="AC30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="R31" t="s">
+        <v>5</v>
       </c>
       <c r="S31" t="s">
-        <v>5</v>
-      </c>
-      <c r="T31" t="s">
         <v>9</v>
       </c>
       <c r="U31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="X31" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>18</v>
       </c>
       <c r="AC31" t="s">
         <v>19</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S32" t="s">
         <v>5</v>
@@ -1527,27 +1560,33 @@
         <v>9</v>
       </c>
       <c r="U32" t="s">
+        <v>20</v>
+      </c>
+      <c r="W32" t="s">
+        <v>14</v>
+      </c>
+      <c r="X32" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y32" t="s">
         <v>14</v>
       </c>
       <c r="Z32" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>18</v>
+        <v>18</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="S33" t="s">
         <v>5</v>
@@ -1556,184 +1595,187 @@
         <v>9</v>
       </c>
       <c r="U33" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="V33" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="W33" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="X33" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>14</v>
       </c>
       <c r="AF33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="S34" t="s">
+        <v>5</v>
       </c>
       <c r="T34" t="s">
-        <v>5</v>
-      </c>
-      <c r="U34" t="s">
-        <v>9</v>
-      </c>
-      <c r="V34" t="s">
-        <v>14</v>
-      </c>
-      <c r="W34" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="X34" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA34" t="s">
         <v>18</v>
       </c>
       <c r="AF34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="S35" t="s">
+        <v>5</v>
       </c>
       <c r="T35" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" t="s">
         <v>9</v>
       </c>
       <c r="X35" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z35" t="s">
         <v>18</v>
       </c>
       <c r="AF35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="T36" t="s">
+        <v>5</v>
       </c>
       <c r="U36" t="s">
-        <v>5</v>
-      </c>
-      <c r="V36" t="s">
         <v>9</v>
       </c>
       <c r="X36" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Z36" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC36" t="s">
         <v>18</v>
       </c>
       <c r="AF36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="T37" t="s">
+        <v>5</v>
       </c>
       <c r="U37" t="s">
-        <v>5</v>
-      </c>
-      <c r="V37" t="s">
-        <v>9</v>
-      </c>
-      <c r="X37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF37" t="s">
-        <v>19</v>
+        <v>9</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>18</v>
       </c>
       <c r="AG37" t="s">
         <v>19</v>
-      </c>
-      <c r="AH37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI37" t="s">
-        <v>19</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="T38" t="s">
+        <v>5</v>
       </c>
       <c r="U38" t="s">
-        <v>5</v>
-      </c>
-      <c r="V38" t="s">
-        <v>9</v>
-      </c>
-      <c r="X38" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s">
         <v>14</v>
       </c>
       <c r="AC38" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD38" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>18</v>
+        <v>18</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="U39" t="s">
         <v>5</v>
@@ -1742,267 +1784,399 @@
         <v>9</v>
       </c>
       <c r="Y39" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Z39" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA39" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>13</v>
+      </c>
+      <c r="U40" t="s">
+        <v>5</v>
       </c>
       <c r="V40" t="s">
-        <v>5</v>
-      </c>
-      <c r="W40" t="s">
         <v>9</v>
       </c>
       <c r="Y40" t="s">
-        <v>14</v>
+        <v>25</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>25</v>
       </c>
       <c r="AA40" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AB40" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>14</v>
       </c>
       <c r="AJ40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="U41" t="s">
+        <v>5</v>
       </c>
       <c r="V41" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" t="s">
         <v>9</v>
       </c>
       <c r="AB41" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC41" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AD41" t="s">
         <v>18</v>
       </c>
       <c r="AJ41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="U42" t="s">
+        <v>5</v>
       </c>
       <c r="V42" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" t="s">
         <v>9</v>
       </c>
       <c r="AB42" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s">
         <v>14</v>
       </c>
       <c r="AD42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE42" t="s">
         <v>18</v>
       </c>
       <c r="AJ42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="V43" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>14</v>
       </c>
       <c r="AE43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF43" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH43" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="V44" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>20</v>
       </c>
       <c r="AE44" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AF44" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK44" t="s">
         <v>19</v>
-      </c>
-      <c r="AL44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM44" t="s">
-        <v>19</v>
-      </c>
-      <c r="AN44" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>5</v>
+        <v>24</v>
+      </c>
+      <c r="V45" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>20</v>
       </c>
       <c r="AF45" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AG45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK45" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
       </c>
-      <c r="AE46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>9</v>
-      </c>
       <c r="AG46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN46" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO46" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>68</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
         <v>27</v>
       </c>
+      <c r="AG48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>76</v>
+      </c>
+      <c r="C49" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
-        <v>29</v>
+      <c r="AG49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO49" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test_new3.4-wide.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -657,7 +663,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -677,13 +683,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -703,13 +709,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -729,13 +738,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -758,10 +773,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -781,7 +796,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -793,7 +808,7 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -813,7 +828,10 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
@@ -825,7 +843,7 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -845,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>14</v>
@@ -860,7 +878,7 @@
         <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -871,17 +889,20 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
@@ -892,10 +913,10 @@
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +927,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -915,16 +936,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
@@ -936,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -956,7 +977,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" t="s">
         <v>14</v>
@@ -971,7 +992,7 @@
         <v>14</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -982,7 +1003,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -991,16 +1012,16 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" t="s">
         <v>14</v>
       </c>
       <c r="Q13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1011,7 +1032,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1023,10 +1044,10 @@
         <v>14</v>
       </c>
       <c r="L14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1037,7 +1058,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1049,10 +1070,10 @@
         <v>14</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1063,7 +1084,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1072,16 +1093,16 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1092,7 +1113,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
@@ -1101,16 +1122,16 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1142,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O18" t="s">
         <v>5</v>
@@ -1139,10 +1160,10 @@
         <v>14</v>
       </c>
       <c r="T18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1162,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="Q19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s">
         <v>14</v>
@@ -1177,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="X19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1188,7 +1209,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
         <v>5</v>
@@ -1197,16 +1218,16 @@
         <v>9</v>
       </c>
       <c r="Q20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T20" t="s">
         <v>14</v>
       </c>
       <c r="U20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1217,7 +1238,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O21" t="s">
         <v>5</v>
@@ -1226,16 +1247,16 @@
         <v>9</v>
       </c>
       <c r="Q21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21" t="s">
         <v>14</v>
       </c>
       <c r="S21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1246,7 +1267,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P22" t="s">
         <v>5</v>
@@ -1255,16 +1276,16 @@
         <v>9</v>
       </c>
       <c r="R22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S22" t="s">
         <v>14</v>
       </c>
       <c r="T22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1275,7 +1296,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P23" t="s">
         <v>5</v>
@@ -1284,16 +1305,16 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T23" t="s">
         <v>14</v>
       </c>
       <c r="U23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1304,7 +1325,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P24" t="s">
         <v>5</v>
@@ -1313,16 +1334,16 @@
         <v>9</v>
       </c>
       <c r="R24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U24" t="s">
         <v>14</v>
       </c>
       <c r="V24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1333,7 +1354,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="s">
         <v>5</v>
@@ -1342,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="S25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T25" t="s">
         <v>14</v>
@@ -1354,10 +1375,10 @@
         <v>14</v>
       </c>
       <c r="W25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1377,10 +1398,10 @@
         <v>9</v>
       </c>
       <c r="S26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1395,7 +1416,7 @@
         <v>14</v>
       </c>
       <c r="AB26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1406,7 +1427,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="s">
         <v>5</v>
@@ -1415,16 +1436,16 @@
         <v>9</v>
       </c>
       <c r="T27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W27" t="s">
         <v>14</v>
       </c>
       <c r="X27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1435,7 +1456,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="s">
         <v>5</v>
@@ -1444,16 +1465,16 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U28" t="s">
         <v>14</v>
       </c>
       <c r="V28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1464,7 +1485,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R29" t="s">
         <v>5</v>
@@ -1473,16 +1494,19 @@
         <v>9</v>
       </c>
       <c r="T29" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="U29" t="s">
+        <v>15</v>
       </c>
       <c r="V29" t="s">
         <v>14</v>
       </c>
       <c r="W29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1493,7 +1517,7 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R30" t="s">
         <v>5</v>
@@ -1502,16 +1526,16 @@
         <v>9</v>
       </c>
       <c r="U30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W30" t="s">
         <v>14</v>
       </c>
       <c r="X30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1522,7 +1546,7 @@
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R31" t="s">
         <v>5</v>
@@ -1531,16 +1555,16 @@
         <v>9</v>
       </c>
       <c r="U31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X31" t="s">
         <v>14</v>
       </c>
       <c r="Y31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1551,7 +1575,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S32" t="s">
         <v>5</v>
@@ -1560,7 +1584,7 @@
         <v>9</v>
       </c>
       <c r="U32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W32" t="s">
         <v>14</v>
@@ -1572,10 +1596,10 @@
         <v>14</v>
       </c>
       <c r="Z32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1595,16 +1619,16 @@
         <v>9</v>
       </c>
       <c r="U33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="X33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB33" t="s">
         <v>14</v>
@@ -1619,7 +1643,7 @@
         <v>14</v>
       </c>
       <c r="AF33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1630,7 +1654,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S34" t="s">
         <v>5</v>
@@ -1639,16 +1663,16 @@
         <v>9</v>
       </c>
       <c r="X34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="s">
         <v>14</v>
       </c>
       <c r="AA34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1659,7 +1683,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S35" t="s">
         <v>5</v>
@@ -1668,16 +1692,16 @@
         <v>9</v>
       </c>
       <c r="X35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s">
         <v>14</v>
       </c>
       <c r="Z35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1688,7 +1712,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T36" t="s">
         <v>5</v>
@@ -1697,16 +1721,19 @@
         <v>9</v>
       </c>
       <c r="X36" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>15</v>
       </c>
       <c r="Z36" t="s">
         <v>14</v>
       </c>
       <c r="AA36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1717,7 +1744,7 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T37" t="s">
         <v>5</v>
@@ -1726,16 +1753,16 @@
         <v>9</v>
       </c>
       <c r="Y37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s">
         <v>14</v>
       </c>
       <c r="AB37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1746,7 +1773,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T38" t="s">
         <v>5</v>
@@ -1755,16 +1782,16 @@
         <v>9</v>
       </c>
       <c r="Y38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB38" t="s">
         <v>14</v>
       </c>
       <c r="AC38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1775,7 +1802,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U39" t="s">
         <v>5</v>
@@ -1784,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="Y39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s">
         <v>14</v>
@@ -1796,10 +1823,10 @@
         <v>14</v>
       </c>
       <c r="AC39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1819,16 +1846,16 @@
         <v>9</v>
       </c>
       <c r="Y40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Z40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF40" t="s">
         <v>14</v>
@@ -1843,7 +1870,7 @@
         <v>14</v>
       </c>
       <c r="AJ40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1854,7 +1881,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U41" t="s">
         <v>5</v>
@@ -1863,16 +1890,16 @@
         <v>9</v>
       </c>
       <c r="AB41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC41" t="s">
         <v>14</v>
       </c>
       <c r="AD41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1883,7 +1910,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U42" t="s">
         <v>5</v>
@@ -1892,16 +1919,16 @@
         <v>9</v>
       </c>
       <c r="AB42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC42" t="s">
         <v>14</v>
       </c>
       <c r="AD42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1912,7 +1939,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V43" t="s">
         <v>5</v>
@@ -1921,16 +1948,19 @@
         <v>9</v>
       </c>
       <c r="AB43" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>15</v>
       </c>
       <c r="AD43" t="s">
         <v>14</v>
       </c>
       <c r="AE43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -1941,7 +1971,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V44" t="s">
         <v>5</v>
@@ -1950,16 +1980,16 @@
         <v>9</v>
       </c>
       <c r="AC44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE44" t="s">
         <v>14</v>
       </c>
       <c r="AF44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -1970,7 +2000,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V45" t="s">
         <v>5</v>
@@ -1979,16 +2009,16 @@
         <v>9</v>
       </c>
       <c r="AC45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF45" t="s">
         <v>14</v>
       </c>
       <c r="AG45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -1999,7 +2029,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG46" t="s">
         <v>5</v>
@@ -2017,7 +2047,7 @@
         <v>14</v>
       </c>
       <c r="AL46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -2037,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="AI47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ47" t="s">
         <v>14</v>
@@ -2052,7 +2082,7 @@
         <v>14</v>
       </c>
       <c r="AN47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -2063,7 +2093,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG48" t="s">
         <v>5</v>
@@ -2072,16 +2102,16 @@
         <v>9</v>
       </c>
       <c r="AI48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s">
         <v>14</v>
       </c>
       <c r="AM48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -2092,7 +2122,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG49" t="s">
         <v>5</v>
@@ -2101,18 +2131,18 @@
         <v>9</v>
       </c>
       <c r="AI49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN49" t="s">
         <v>14</v>
       </c>
       <c r="AO49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -2120,7 +2150,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
@@ -2128,15 +2158,15 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
@@ -2144,39 +2174,55 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" t="s">
         <v>39</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
